--- a/resultado_nao_formatado.xlsx
+++ b/resultado_nao_formatado.xlsx
@@ -446,22 +446,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Média direto</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Média indireto</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Média direto</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>P-value Indirect/Direct</t>
+          <t>P-value Direct/Indirect</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Effect Size Indirect/Direct</t>
+          <t>Effect Size Direct/Indirect</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -481,27 +481,27 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Effect Size Big/Small</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Média Especialista</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Média Não-Especialista</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>P-value Specialist/Non-Specialist</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Effect Size Specialist/Non-Specialist</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Média Especialista</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Média Não-Especialista</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>P-value Specialist/Non-Specialist</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Effect Size Especialista/Não-Especialista</t>
         </is>
       </c>
     </row>
@@ -517,48 +517,48 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12.9635685599541</v>
+        <v>3.084337349397591</v>
       </c>
       <c r="D2" t="n">
-        <v>6.846938775510203</v>
+        <v>3.596491228070176</v>
       </c>
       <c r="E2" t="n">
-        <v>15.03533026113671</v>
+        <v>3.4</v>
       </c>
       <c r="F2" t="n">
-        <v>3.602709037418849e-05</v>
+        <v>0.3726463063168448</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>(0.5821812596006144, 'large')</t>
+          <t>(0.05380116959064327, 'negligible')</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>12.99194139194139</v>
+        <v>3.618181818181818</v>
       </c>
       <c r="I2" t="n">
-        <v>13.37053571428571</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="J2" t="n">
-        <v>0.591578852630622</v>
+        <v>0.3350249944387612</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>(-0.03653846153846154, 'negligible')</t>
+          <t>(0.0703030303030303, 'negligible')</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>11.50457875457876</v>
+        <v>3.090909090909091</v>
       </c>
       <c r="M2" t="n">
-        <v>13.62907268170426</v>
+        <v>3.76</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8335340976221617</v>
+        <v>0.9920700764609476</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>(-0.13225371120107962, 'negligible')</t>
+          <t>(-0.34363636363636363, 'medium')</t>
         </is>
       </c>
     </row>
@@ -574,48 +574,48 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11.06741250717154</v>
+        <v>2.457831325301205</v>
       </c>
       <c r="D3" t="n">
-        <v>5.051020408163266</v>
+        <v>3.283018867924528</v>
       </c>
       <c r="E3" t="n">
-        <v>13.10522273425499</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>9.023332819947824e-05</v>
+        <v>0.1806241396079169</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>(0.5460829493087558, 'large')</t>
+          <t>(0.17735849056603772, 'small')</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>11.02014652014652</v>
+        <v>3.244897959183673</v>
       </c>
       <c r="I3" t="n">
-        <v>11.39285714285714</v>
+        <v>3.230769230769231</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5095256390862428</v>
+        <v>0.3969205100110033</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>(-0.0028846153846153848, 'negligible')</t>
+          <t>(0.04709576138147567, 'negligible')</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>9.720695970695969</v>
+        <v>3.1875</v>
       </c>
       <c r="M3" t="n">
-        <v>11.68170426065163</v>
+        <v>3.25531914893617</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8119067719883595</v>
+        <v>0.4704357995235507</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>(-0.12010796221322537, 'negligible')</t>
+          <t>(0.013297872340425532, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -631,48 +631,48 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.469305794607</v>
+        <v>2.349397590361446</v>
       </c>
       <c r="D4" t="n">
-        <v>4.566893424036281</v>
+        <v>3.111111111111111</v>
       </c>
       <c r="E4" t="n">
-        <v>12.46850998463902</v>
+        <v>2.454545454545455</v>
       </c>
       <c r="F4" t="n">
-        <v>4.588374219948168e-05</v>
+        <v>0.02065558980934877</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>(0.5714285714285714, 'large')</t>
+          <t>(0.3602693602693603, 'medium')</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>10.17289377289377</v>
+        <v>2.96</v>
       </c>
       <c r="I4" t="n">
-        <v>11.73214285714286</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6746767899378527</v>
+        <v>0.705593313416951</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>(-0.07211538461538461, 'negligible')</t>
+          <t>(-0.08571428571428572, 'negligible')</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>9.13003663003663</v>
+        <v>2.888888888888889</v>
       </c>
       <c r="M4" t="n">
-        <v>11.08020050125313</v>
+        <v>3.042553191489362</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8788834359101817</v>
+        <v>0.6906386548290177</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>(-0.1592442645074224, 'small')</t>
+          <t>(-0.07210401891252956, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -688,48 +688,48 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.25243832472748</v>
+        <v>2.493975903614458</v>
       </c>
       <c r="D5" t="n">
-        <v>5.590702947845805</v>
+        <v>3.051724137931035</v>
       </c>
       <c r="E5" t="n">
-        <v>13.17012288786482</v>
+        <v>2.727272727272727</v>
       </c>
       <c r="F5" t="n">
-        <v>5.457128292149657e-05</v>
+        <v>0.1984848858042937</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>(0.5668202764976958, 'large')</t>
+          <t>(0.15830721003134796, 'small')</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>11.4978021978022</v>
+        <v>3.074074074074074</v>
       </c>
       <c r="I5" t="n">
-        <v>10.82886904761905</v>
+        <v>2.785714285714286</v>
       </c>
       <c r="J5" t="n">
-        <v>0.389989875324071</v>
+        <v>0.1735315067680593</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>(0.046153846153846156, 'negligible')</t>
+          <t>(0.16005291005291006, 'small')</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>11.0485347985348</v>
+        <v>2.863636363636364</v>
       </c>
       <c r="M5" t="n">
-        <v>11.34544695071011</v>
+        <v>3.063829787234043</v>
       </c>
       <c r="N5" t="n">
-        <v>0.564500980017931</v>
+        <v>0.7231318065260695</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>(-0.021592442645074223, 'negligible')</t>
+          <t>(-0.0851063829787234, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -745,48 +745,48 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11.86632243258749</v>
+        <v>2.602409638554217</v>
       </c>
       <c r="D6" t="n">
-        <v>5.88095238095238</v>
+        <v>3.189655172413793</v>
       </c>
       <c r="E6" t="n">
-        <v>13.89362519201229</v>
+        <v>3.1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0001229125012441675</v>
+        <v>0.4574813087110049</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>(0.5368663594470046, 'large')</t>
+          <t>(0.022413793103448276, 'negligible')</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11.67728937728938</v>
+        <v>3.192307692307693</v>
       </c>
       <c r="I6" t="n">
-        <v>12.47023809523809</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5801602480960015</v>
+        <v>0.4456015311617267</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>(-0.03173076923076923, 'negligible')</t>
+          <t>(0.024725274725274724, 'negligible')</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12.76831501831502</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>11.45488721804511</v>
+        <v>3.266666666666667</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2406914482037043</v>
+        <v>0.7879569772647925</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>(0.09716599190283401, 'negligible')</t>
+          <t>(-0.11497584541062802, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -802,48 +802,48 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.81698221457258</v>
+        <v>2.445783132530121</v>
       </c>
       <c r="D7" t="n">
-        <v>5.589569160997732</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="E7" t="n">
-        <v>12.58755760368664</v>
+        <v>2.909090909090909</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000317088872726518</v>
+        <v>0.2956921913976033</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>(0.49923195084485406, 'large')</t>
+          <t>(0.09932659932659933, 'negligible')</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10.44761904761905</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="I7" t="n">
-        <v>12.28720238095238</v>
+        <v>3.214285714285714</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7913461541744429</v>
+        <v>0.5899747941498303</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>(-0.12980769230769232, 'negligible')</t>
+          <t>(-0.03644314868804665, 'negligible')</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>11.80952380952381</v>
+        <v>3.095238095238095</v>
       </c>
       <c r="M7" t="n">
-        <v>10.36424394319131</v>
+        <v>3.136363636363636</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2542431770780896</v>
+        <v>0.4527417841877206</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>(0.09109311740890688, 'negligible')</t>
+          <t>(0.0183982683982684, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -859,48 +859,48 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12.97475616752725</v>
+        <v>2.951807228915662</v>
       </c>
       <c r="D8" t="n">
-        <v>7.179138321995465</v>
+        <v>3.482758620689655</v>
       </c>
       <c r="E8" t="n">
-        <v>14.93778801843318</v>
+        <v>3.583333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000132649032141842</v>
+        <v>0.6104287967573402</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>(0.5345622119815668, 'large')</t>
+          <t>(-0.04741379310344827, 'negligible')</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>12.77142857142857</v>
+        <v>3.509433962264151</v>
       </c>
       <c r="I8" t="n">
-        <v>13.77529761904762</v>
+        <v>3.533333333333333</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6763965415476558</v>
+        <v>0.5155474577561279</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>(-0.07307692307692308, 'negligible')</t>
+          <t>(-0.005031446540880503, 'negligible')</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>13.35714285714286</v>
+        <v>3.363636363636364</v>
       </c>
       <c r="M8" t="n">
-        <v>12.80033416875522</v>
+        <v>3.5625</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3487995491384355</v>
+        <v>0.7441613142972103</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>(0.05398110661268556, 'negligible')</t>
+          <t>(-0.09185606060606061, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -916,48 +916,48 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12.81353987378084</v>
+        <v>2.867469879518072</v>
       </c>
       <c r="D9" t="n">
-        <v>7.143990929705216</v>
+        <v>3.379310344827586</v>
       </c>
       <c r="E9" t="n">
-        <v>14.73387096774194</v>
+        <v>3.5</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001832646343334184</v>
+        <v>0.6445025770940875</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>(0.522273425499232, 'large')</t>
+          <t>(-0.06465517241379311, 'negligible')</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>13.02014652014652</v>
+        <v>3.518518518518519</v>
       </c>
       <c r="I9" t="n">
-        <v>11.92857142857143</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3321897985921481</v>
+        <v>0.06631735808845449</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>(0.07115384615384615, 'negligible')</t>
+          <t>(0.2552910052910053, 'small')</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>14.75732600732601</v>
+        <v>3.416666666666667</v>
       </c>
       <c r="M9" t="n">
-        <v>11.92690058479532</v>
+        <v>3.391304347826087</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06806994189291339</v>
+        <v>0.5102046229036937</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>(0.20512820512820512, 'small')</t>
+          <t>(-0.002717391304347826, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -973,48 +973,48 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.314974182444061</v>
+        <v>2.096385542168675</v>
       </c>
       <c r="D10" t="n">
-        <v>2.663265306122449</v>
+        <v>3.26530612244898</v>
       </c>
       <c r="E10" t="n">
-        <v>11.56797235023041</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>6.244467619586085e-06</v>
+        <v>0.02862713503093027</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>(0.6290322580645161, 'large')</t>
+          <t>(0.46598639455782315, 'medium')</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>8.75934065934066</v>
+        <v>3.25</v>
       </c>
       <c r="I10" t="n">
-        <v>11.90327380952381</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8795132523646163</v>
+        <v>0.1895748632131497</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>(-0.18557692307692308, 'small')</t>
+          <t>(0.15535714285714286, 'small')</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>9.418498168498166</v>
+        <v>3.058823529411764</v>
       </c>
       <c r="M10" t="n">
-        <v>9.267752715121137</v>
+        <v>3.210526315789474</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4521838087733452</v>
+        <v>0.6914177867990292</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>(0.016869095816464237, 'negligible')</t>
+          <t>(-0.0804953560371517, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -1030,48 +1030,48 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10.91537578886977</v>
+        <v>2.421686746987952</v>
       </c>
       <c r="D11" t="n">
-        <v>5.065759637188209</v>
+        <v>3.264150943396226</v>
       </c>
       <c r="E11" t="n">
-        <v>12.89669738863287</v>
+        <v>2.8</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0001112073540288764</v>
+        <v>0.07578596068194351</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>(0.5384024577572964, 'large')</t>
+          <t>(0.27358490566037735, 'small')</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.79194139194139</v>
+        <v>3.276595744680851</v>
       </c>
       <c r="I11" t="n">
-        <v>11.81547619047619</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6445057667216181</v>
+        <v>0.3014665222542774</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>(-0.058653846153846154, 'negligible')</t>
+          <t>(0.08814589665653495, 'negligible')</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>11.56227106227106</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>10.6203007518797</v>
+        <v>3.292682926829268</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2932853959645596</v>
+        <v>0.8918861349563805</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>(0.07489878542510121, 'negligible')</t>
+          <t>(-0.17849223946784923, 'small')</t>
         </is>
       </c>
     </row>
@@ -1087,48 +1087,48 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11.08892713711991</v>
+        <v>2.590361445783132</v>
       </c>
       <c r="D12" t="n">
-        <v>6.23922902494331</v>
+        <v>3.411764705882353</v>
       </c>
       <c r="E12" t="n">
-        <v>12.7315668202765</v>
+        <v>2.928571428571428</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0006607941029423167</v>
+        <v>0.06216385160055331</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>(0.46927803379416283, 'medium')</t>
+          <t>(0.2619047619047619, 'small')</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>10.99377289377289</v>
+        <v>3.36</v>
       </c>
       <c r="I12" t="n">
-        <v>11.34672619047619</v>
+        <v>3.230769230769231</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5663115823762106</v>
+        <v>0.395973395721591</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>(-0.025961538461538463, 'negligible')</t>
+          <t>(0.047692307692307694, 'negligible')</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10.86904761904762</v>
+        <v>3.1</v>
       </c>
       <c r="M12" t="n">
-        <v>11.18922305764411</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5373468124085397</v>
+        <v>0.8536943490739011</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>(-0.012145748987854251, 'negligible')</t>
+          <t>(-0.15777777777777777, 'small')</t>
         </is>
       </c>
     </row>
@@ -1144,48 +1144,48 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.633964429145152</v>
+        <v>2.012048192771084</v>
       </c>
       <c r="D13" t="n">
-        <v>4.53968253968254</v>
+        <v>3.065217391304348</v>
       </c>
       <c r="E13" t="n">
-        <v>10.02073732718894</v>
+        <v>2.888888888888889</v>
       </c>
       <c r="F13" t="n">
-        <v>0.004365380218459855</v>
+        <v>0.4060663243508396</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>(0.3778801843317972, 'medium')</t>
+          <t>(0.050724637681159424, 'negligible')</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>8.621245421245421</v>
+        <v>3.095238095238095</v>
       </c>
       <c r="I13" t="n">
-        <v>9.764880952380953</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7560505625515628</v>
+        <v>0.3702702533186408</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>(-0.10961538461538461, 'negligible')</t>
+          <t>(0.06043956043956044, 'negligible')</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6.12087912087912</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>9.780284043441938</v>
+        <v>3.219512195121951</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9676454477837543</v>
+        <v>0.9846057696705625</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>(-0.2483130904183536, 'small')</t>
+          <t>(-0.3710801393728223, 'medium')</t>
         </is>
       </c>
     </row>
@@ -1201,48 +1201,48 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11.61101549053356</v>
+        <v>2.63855421686747</v>
       </c>
       <c r="D14" t="n">
-        <v>6.531746031746032</v>
+        <v>3.377358490566038</v>
       </c>
       <c r="E14" t="n">
-        <v>13.33141321044547</v>
+        <v>3.076923076923077</v>
       </c>
       <c r="F14" t="n">
-        <v>0.000743809239513133</v>
+        <v>0.1745822268591613</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>(0.4646697388632873, 'medium')</t>
+          <t>(0.16400580551523947, 'small')</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>11.75824175824176</v>
+        <v>3.411764705882353</v>
       </c>
       <c r="I14" t="n">
-        <v>11.21428571428571</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3694036870072362</v>
+        <v>0.1091163358768145</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>(0.05480769230769231, 'negligible')</t>
+          <t>(0.21008403361344538, 'small')</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>12.74450549450549</v>
+        <v>3.380952380952381</v>
       </c>
       <c r="M14" t="n">
-        <v>11.09398496240602</v>
+        <v>3.288888888888889</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1669371376545493</v>
+        <v>0.3958554515677144</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>(0.1329284750337382, 'negligible')</t>
+          <t>(0.04021164021164021, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -1258,48 +1258,48 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10.62564543889845</v>
+        <v>2.506024096385542</v>
       </c>
       <c r="D15" t="n">
-        <v>7.515873015873015</v>
+        <v>3.24</v>
       </c>
       <c r="E15" t="n">
-        <v>11.678955453149</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02408243742087129</v>
+        <v>0.5171505464736408</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>(0.2887864823348694, 'small')</t>
+          <t>(-0.005714285714285714, 'negligible')</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.35128205128205</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="I15" t="n">
-        <v>11.42113095238095</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6982487424534143</v>
+        <v>0.2731523645105361</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>(-0.08269230769230769, 'negligible')</t>
+          <t>(0.10267857142857142, 'negligible')</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>11.65659340659341</v>
+        <v>3.55</v>
       </c>
       <c r="M15" t="n">
-        <v>10.15538847117794</v>
+        <v>3.113636363636364</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2161499792108474</v>
+        <v>0.1028141268689159</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>(0.10796221322537113, 'negligible')</t>
+          <t>(0.18863636363636363, 'small')</t>
         </is>
       </c>
     </row>
@@ -1315,48 +1315,48 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10.01864601262192</v>
+        <v>2.19277108433735</v>
       </c>
       <c r="D16" t="n">
-        <v>4.814058956916099</v>
+        <v>3.224489795918367</v>
       </c>
       <c r="E16" t="n">
-        <v>11.78149001536099</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0003071595568577452</v>
+        <v>0.09089089967232311</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>(0.49615975422427033, 'large')</t>
+          <t>(0.2766439909297052, 'small')</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9.944688644688645</v>
+        <v>3.177777777777778</v>
       </c>
       <c r="I16" t="n">
-        <v>10.32142857142857</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5167778445610181</v>
+        <v>0.3475074753753823</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>(-0.0057692307692307696, 'negligible')</t>
+          <t>(0.07407407407407407, 'negligible')</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>10.84065934065934</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="M16" t="n">
-        <v>9.643692564745196</v>
+        <v>3.125</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3361164553324871</v>
+        <v>0.37793159953203</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>(0.058029689608636977, 'negligible')</t>
+          <t>(0.05138888888888889, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -1372,48 +1372,48 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9.72231784279977</v>
+        <v>2.144578313253012</v>
       </c>
       <c r="D17" t="n">
-        <v>5.382086167800454</v>
+        <v>3.02</v>
       </c>
       <c r="E17" t="n">
-        <v>11.19239631336405</v>
+        <v>3.375</v>
       </c>
       <c r="F17" t="n">
-        <v>0.002033021878963032</v>
+        <v>0.7855416490168075</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>(0.4162826420890937, 'medium')</t>
+          <t>(-0.1675, 'small')</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>9.978754578754581</v>
+        <v>3.177777777777778</v>
       </c>
       <c r="I17" t="n">
-        <v>8.645833333333332</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2353974543305304</v>
+        <v>0.1425141583880039</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>(0.11634615384615385, 'negligible')</t>
+          <t>(0.19814814814814816, 'small')</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9.398351648351648</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>9.870091896407686</v>
+        <v>3.097560975609756</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5573879192541743</v>
+        <v>0.6509020265525297</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>(-0.018893387314439947, 'negligible')</t>
+          <t>(-0.06169296987087518, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -1429,48 +1429,48 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15.96213425129088</v>
+        <v>3.819277108433735</v>
       </c>
       <c r="D18" t="n">
-        <v>8.780045351473923</v>
+        <v>4.2</v>
       </c>
       <c r="E18" t="n">
-        <v>18.39477726574501</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>3.821971912617211e-06</v>
+        <v>0.6690476158930665</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>(0.6566820276497696, 'large')</t>
+          <t>(-0.06666666666666667, 'negligible')</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>15.73076923076923</v>
+        <v>4.189655172413793</v>
       </c>
       <c r="I18" t="n">
-        <v>16.56845238095238</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6992390569132386</v>
+        <v>0.7830407366509105</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>(-0.08365384615384615, 'negligible')</t>
+          <t>(-0.1206896551724138, 'negligible')</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>15.50732600732601</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>16.16959064327485</v>
+        <v>4.326923076923077</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7336050956086105</v>
+        <v>0.966244619991062</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>(-0.08502024291497975, 'negligible')</t>
+          <t>(-0.24498327759197325, 'small')</t>
         </is>
       </c>
     </row>
@@ -1486,48 +1486,48 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14.55622489959839</v>
+        <v>3.240963855421687</v>
       </c>
       <c r="D19" t="n">
-        <v>6.689342403628117</v>
+        <v>4.181818181818182</v>
       </c>
       <c r="E19" t="n">
-        <v>17.22081413210445</v>
+        <v>3.9</v>
       </c>
       <c r="F19" t="n">
-        <v>2.304006821442376e-05</v>
+        <v>0.2152810391892057</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>(0.5952380952380952, 'large')</t>
+          <t>(0.14909090909090908, 'small')</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>14.69377289377289</v>
+        <v>4.22</v>
       </c>
       <c r="I19" t="n">
-        <v>14.15029761904762</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3942921302262595</v>
+        <v>0.2220052416458971</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>(0.04423076923076923, 'negligible')</t>
+          <t>(0.12714285714285714, 'negligible')</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>12.87179487179487</v>
+        <v>3.941176470588236</v>
       </c>
       <c r="M19" t="n">
-        <v>15.32456140350877</v>
+        <v>4.208333333333333</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8060732316646975</v>
+        <v>0.9440661980382037</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>(-0.11740890688259109, 'negligible')</t>
+          <t>(-0.2426470588235294, 'small')</t>
         </is>
       </c>
     </row>
@@ -1543,48 +1543,48 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13.94377510040161</v>
+        <v>3.192771084337349</v>
       </c>
       <c r="D20" t="n">
-        <v>7.672335600907029</v>
+        <v>3.824561403508772</v>
       </c>
       <c r="E20" t="n">
-        <v>16.06797235023041</v>
+        <v>3.916666666666667</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001007771821808315</v>
+        <v>0.5915044232504775</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>(0.5445468509984639, 'large')</t>
+          <t>(-0.039473684210526314, 'negligible')</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>14.14065934065934</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="I20" t="n">
-        <v>13.22023809523809</v>
+        <v>3.642857142857143</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2922567638134047</v>
+        <v>0.3258656311287144</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>(0.08942307692307692, 'negligible')</t>
+          <t>(0.07671957671957672, 'negligible')</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>13.24267399267399</v>
+        <v>3.7</v>
       </c>
       <c r="M20" t="n">
-        <v>14.26357560568087</v>
+        <v>3.897959183673469</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7323836038205481</v>
+        <v>0.8243702144896332</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>(-0.08434547908232119, 'negligible')</t>
+          <t>(-0.13673469387755102, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -1600,48 +1600,48 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15.47102696500287</v>
+        <v>3.578313253012048</v>
       </c>
       <c r="D21" t="n">
-        <v>9.292517006802722</v>
+        <v>4.137931034482759</v>
       </c>
       <c r="E21" t="n">
-        <v>17.56374807987711</v>
+        <v>4.384615384615385</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0002430923829637859</v>
+        <v>0.7387103205093204</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>(0.511520737327189, 'large')</t>
+          <t>(-0.10477453580901856, 'negligible')</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>15.32564102564102</v>
+        <v>4.181818181818182</v>
       </c>
       <c r="I21" t="n">
-        <v>16.32886904761905</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5730332797231009</v>
+        <v>0.6888950411544035</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>(-0.028846153846153848, 'negligible')</t>
+          <t>(-0.07636363636363637, 'negligible')</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>16.25274725274725</v>
+        <v>4.272727272727272</v>
       </c>
       <c r="M21" t="n">
-        <v>15.11445279866333</v>
+        <v>4.142857142857143</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2960092822836561</v>
+        <v>0.4441855425932394</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>(0.07422402159244265, 'negligible')</t>
+          <t>(0.02040816326530612, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -1657,48 +1657,48 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.4667240390132</v>
+        <v>3.63855421686747</v>
       </c>
       <c r="D22" t="n">
-        <v>7.869614512471655</v>
+        <v>4.448275862068965</v>
       </c>
       <c r="E22" t="n">
-        <v>19.37864823348694</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>6.266120453631796e-06</v>
+        <v>0.05579045652795837</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>(0.6397849462365591, 'large')</t>
+          <t>(0.2727272727272727, 'small')</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>16.35934065934066</v>
+        <v>4.39622641509434</v>
       </c>
       <c r="I22" t="n">
-        <v>16.63244047619047</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4881398851720745</v>
+        <v>0.320113998552045</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>(0.0057692307692307696, 'negligible')</t>
+          <t>(0.07412398921832884, 'negligible')</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>16.93315018315019</v>
+        <v>4.318181818181818</v>
       </c>
       <c r="M22" t="n">
-        <v>16.25396825396825</v>
+        <v>4.404255319148936</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4686213808070494</v>
+        <v>0.7928558977857513</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>(0.011470985155195682, 'negligible')</t>
+          <t>(-0.10831721470019343, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -1714,48 +1714,48 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.55421686746988</v>
+        <v>3.542168674698795</v>
       </c>
       <c r="D23" t="n">
-        <v>9.098639455782312</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="E23" t="n">
-        <v>17.74078341013824</v>
+        <v>4.153846153846154</v>
       </c>
       <c r="F23" t="n">
-        <v>5.113442590028875e-05</v>
+        <v>0.0996589630080576</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>(0.5691244239631337, 'large')</t>
+          <t>(0.21153846153846154, 'small')</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>15.35494505494506</v>
+        <v>4.264150943396227</v>
       </c>
       <c r="I23" t="n">
-        <v>15.97916666666667</v>
+        <v>4.214285714285714</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5094887028006196</v>
+        <v>0.6255138365626866</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>(-0.0028846153846153848, 'negligible')</t>
+          <t>(-0.04986522911051213, 'negligible')</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>15.02106227106227</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
-        <v>15.79741019214703</v>
+        <v>4.375</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6366031720001029</v>
+        <v>0.9424348147016396</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>(-0.04723346828609987, 'negligible')</t>
+          <t>(-0.21825396825396826, 'small')</t>
         </is>
       </c>
     </row>
@@ -1771,48 +1771,48 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.67670682730924</v>
+        <v>3.783132530120481</v>
       </c>
       <c r="D24" t="n">
-        <v>9.980725623582765</v>
+        <v>4.288135593220339</v>
       </c>
       <c r="E24" t="n">
-        <v>18.94470046082949</v>
+        <v>4.357142857142857</v>
       </c>
       <c r="F24" t="n">
-        <v>4.217705870432343e-05</v>
+        <v>0.4050097612986614</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>(0.5768049155145929, 'large')</t>
+          <t>(0.0387409200968523, 'negligible')</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>16.57399267399267</v>
+        <v>4.298245614035087</v>
       </c>
       <c r="I24" t="n">
-        <v>16.43303571428572</v>
+        <v>4.214285714285714</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5401967698296997</v>
+        <v>0.348392608100787</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>(-0.015384615384615385, 'negligible')</t>
+          <t>(0.06265664160401002, 'negligible')</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>16.58882783882784</v>
+        <v>4.181818181818182</v>
       </c>
       <c r="M24" t="n">
-        <v>16.71679197994987</v>
+        <v>4.352941176470588</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5078404401725847</v>
+        <v>0.8172442457622354</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>(-0.0020242914979757085, 'negligible')</t>
+          <t>(-0.12032085561497326, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -1828,48 +1828,48 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.03040734366036</v>
+        <v>3.662650602409639</v>
       </c>
       <c r="D25" t="n">
-        <v>8.630385487528345</v>
+        <v>4.169491525423729</v>
       </c>
       <c r="E25" t="n">
-        <v>18.536866359447</v>
+        <v>4.142857142857143</v>
       </c>
       <c r="F25" t="n">
-        <v>1.112213277643536e-05</v>
+        <v>0.2916815135042219</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>(0.6221198156682027, 'large')</t>
+          <t>(0.08958837772397095, 'negligible')</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>15.56886446886447</v>
+        <v>4.071428571428571</v>
       </c>
       <c r="I25" t="n">
-        <v>17.16369047619047</v>
+        <v>4.4</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8258975201646988</v>
+        <v>0.869003811087273</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>(-0.15096153846153845, 'small')</t>
+          <t>(-0.1761904761904762, 'small')</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>17.63186813186813</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="M25" t="n">
-        <v>15.2999164578112</v>
+        <v>4.204081632653061</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1522182455402736</v>
+        <v>0.611548930352069</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>(0.1417004048582996, 'negligible')</t>
+          <t>(-0.03741496598639456, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -1885,48 +1885,48 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10.58347676419966</v>
+        <v>2.385542168674699</v>
       </c>
       <c r="D26" t="n">
-        <v>4.365079365079365</v>
+        <v>3.384615384615385</v>
       </c>
       <c r="E26" t="n">
-        <v>12.68970814132104</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="F26" t="n">
-        <v>7.039465737845116e-05</v>
+        <v>0.2810756282237484</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>(0.5522273425499232, 'large')</t>
+          <t>(0.1346153846153846, 'negligible')</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>9.904395604395605</v>
+        <v>3.348837209302326</v>
       </c>
       <c r="I26" t="n">
-        <v>13.41517857142857</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0.928411648413193</v>
+        <v>0.5725255127678833</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>(-0.23365384615384616, 'small')</t>
+          <t>(-0.02945736434108527, 'negligible')</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>10.05128205128205</v>
+        <v>3.294117647058823</v>
       </c>
       <c r="M26" t="n">
-        <v>10.82623224728488</v>
+        <v>3.380952380952381</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6210007736888242</v>
+        <v>0.6349129355114269</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>(-0.04116059379217274, 'negligible')</t>
+          <t>(-0.0546218487394958, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -1942,48 +1942,48 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15.06253585771658</v>
+        <v>3.481927710843373</v>
       </c>
       <c r="D27" t="n">
-        <v>9.032879818594102</v>
+        <v>4.142857142857143</v>
       </c>
       <c r="E27" t="n">
-        <v>17.10483870967742</v>
+        <v>4.384615384615385</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0002864709186321362</v>
+        <v>0.8392598895185552</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>(0.5046082949308756, 'large')</t>
+          <t>(-0.16346153846153846, 'small')</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>14.8014652014652</v>
+        <v>4.235294117647059</v>
       </c>
       <c r="I27" t="n">
-        <v>16.09375</v>
+        <v>4.0625</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5</v>
+        <v>0.4059068807824879</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>(0.0009615384615384616, 'negligible')</t>
+          <t>(0.03799019607843137, 'negligible')</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>14.85805860805861</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
-        <v>15.15580618212197</v>
+        <v>4.276595744680851</v>
       </c>
       <c r="N27" t="n">
-        <v>0.697319463295735</v>
+        <v>0.9559367762000509</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>(-0.07017543859649122, 'negligible')</t>
+          <t>(-0.2369439071566731, 'small')</t>
         </is>
       </c>
     </row>
@@ -1999,48 +1999,48 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14.91939185312679</v>
+        <v>3.481927710843373</v>
       </c>
       <c r="D28" t="n">
-        <v>9.331065759637188</v>
+        <v>4.346153846153846</v>
       </c>
       <c r="E28" t="n">
-        <v>16.81221198156682</v>
+        <v>4.5</v>
       </c>
       <c r="F28" t="n">
-        <v>0.000828843385526084</v>
+        <v>0.5910276643644787</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>(0.46006144393241166, 'medium')</t>
+          <t>(-0.034340659340659344, 'negligible')</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>14.93223443223443</v>
+        <v>4.365384615384615</v>
       </c>
       <c r="I28" t="n">
-        <v>14.40327380952381</v>
+        <v>4.416666666666667</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5261308672238789</v>
+        <v>0.7517386289770782</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>(-0.009615384615384616, 'negligible')</t>
+          <t>(-0.11057692307692307, 'negligible')</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>13.62454212454212</v>
+        <v>4.05</v>
       </c>
       <c r="M28" t="n">
-        <v>15.51002506265664</v>
+        <v>4.521739130434782</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8652901281768137</v>
+        <v>0.9905355534400277</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>(-0.150472334682861, 'small')</t>
+          <t>(-0.32282608695652176, 'small')</t>
         </is>
       </c>
     </row>
@@ -2056,48 +2056,48 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11.13912794033276</v>
+        <v>2.590361445783132</v>
       </c>
       <c r="D29" t="n">
-        <v>5.512471655328797</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="E29" t="n">
-        <v>13.04493087557604</v>
+        <v>3.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.000681765490767967</v>
+        <v>0.05405883845665009</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>(0.46390168970814133, 'medium')</t>
+          <t>(0.3145833333333333, 'small')</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>11.28498168498169</v>
+        <v>3.717391304347826</v>
       </c>
       <c r="I29" t="n">
-        <v>11.93898809523809</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="J29" t="n">
-        <v>0.615627189401005</v>
+        <v>0.468155400853318</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>(-0.046153846153846156, 'negligible')</t>
+          <t>(0.016304347826086956, 'negligible')</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>7.619047619047619</v>
+        <v>3.357142857142857</v>
       </c>
       <c r="M29" t="n">
-        <v>12.74477861319967</v>
+        <v>3.818181818181818</v>
       </c>
       <c r="N29" t="n">
-        <v>0.9896822760444509</v>
+        <v>0.8974250048320671</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>(-0.31309041835357626, 'small')</t>
+          <t>(-0.2159090909090909, 'small')</t>
         </is>
       </c>
     </row>
@@ -2113,48 +2113,48 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>14.1399885255307</v>
+        <v>3.253012048192771</v>
       </c>
       <c r="D30" t="n">
-        <v>9.077097505668933</v>
+        <v>4.076923076923077</v>
       </c>
       <c r="E30" t="n">
-        <v>15.85483870967742</v>
+        <v>4.142857142857143</v>
       </c>
       <c r="F30" t="n">
-        <v>0.001875383930052214</v>
+        <v>0.6402773853482063</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>(0.423963133640553, 'medium')</t>
+          <t>(-0.057692307692307696, 'negligible')</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>14.13260073260073</v>
+        <v>4.134615384615385</v>
       </c>
       <c r="I30" t="n">
-        <v>14.6875</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6033362342347287</v>
+        <v>0.2643001421791115</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>(-0.041346153846153845, 'negligible')</t>
+          <t>(0.10798816568047337, 'negligible')</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>12.31318681318681</v>
+        <v>3.789473684210526</v>
       </c>
       <c r="M30" t="n">
-        <v>14.97326649958229</v>
+        <v>4.212765957446808</v>
       </c>
       <c r="N30" t="n">
-        <v>0.9284503950304526</v>
+        <v>0.9698129641867167</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>(-0.19973009446693657, 'small')</t>
+          <t>(-0.2777155655095185, 'small')</t>
         </is>
       </c>
     </row>
@@ -2170,30 +2170,30 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>15.2289156626506</v>
+        <v>3.566265060240964</v>
       </c>
       <c r="D31" t="n">
-        <v>9.937641723356009</v>
+        <v>4.423076923076923</v>
       </c>
       <c r="E31" t="n">
-        <v>17.02112135176651</v>
+        <v>4.4</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0006476389662511871</v>
+        <v>0.4330267779428367</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>(0.47081413210445466, 'medium')</t>
+          <t>(0.026923076923076925, 'negligible')</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>15.07399267399268</v>
+        <v>4.442307692307693</v>
       </c>
       <c r="I31" t="n">
-        <v>15.43303571428571</v>
+        <v>4.307692307692307</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5023754883607769</v>
+        <v>0.5036681523959258</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2201,17 +2201,17 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>14.62545787545788</v>
+        <v>4.190476190476191</v>
       </c>
       <c r="M31" t="n">
-        <v>15.50417710944027</v>
+        <v>4.521739130434782</v>
       </c>
       <c r="N31" t="n">
-        <v>0.704381769005652</v>
+        <v>0.9913344071766134</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>(-0.0728744939271255, 'negligible')</t>
+          <t>(-0.32401656314699795, 'small')</t>
         </is>
       </c>
     </row>
@@ -2227,48 +2227,48 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11.96844520940907</v>
+        <v>2.674698795180723</v>
       </c>
       <c r="D32" t="n">
-        <v>5.718820861678005</v>
+        <v>3.692307692307693</v>
       </c>
       <c r="E32" t="n">
-        <v>14.0852534562212</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0002326430733366279</v>
+        <v>0.1583323424548489</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>(0.5092165898617511, 'large')</t>
+          <t>(0.20512820512820512, 'small')</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>11.72014652014652</v>
+        <v>3.638297872340425</v>
       </c>
       <c r="I32" t="n">
-        <v>13.22321428571428</v>
+        <v>3.692307692307693</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7271941018121736</v>
+        <v>0.6204965728297285</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>(-0.09615384615384616, 'negligible')</t>
+          <t>(-0.05237315875613748, 'negligible')</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>11.21978021978022</v>
+        <v>3.444444444444445</v>
       </c>
       <c r="M32" t="n">
-        <v>12.30994152046784</v>
+        <v>3.720930232558139</v>
       </c>
       <c r="N32" t="n">
-        <v>0.7003075934542625</v>
+        <v>0.8373278099739079</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>(-0.0708502024291498, 'negligible')</t>
+          <t>(-0.15374677002583978, 'small')</t>
         </is>
       </c>
     </row>
@@ -2284,48 +2284,48 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>13.10126219162364</v>
+        <v>2.867469879518072</v>
       </c>
       <c r="D33" t="n">
-        <v>6.835600907029478</v>
+        <v>3.941176470588236</v>
       </c>
       <c r="E33" t="n">
-        <v>15.22350230414746</v>
+        <v>3.7</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0003786914169483024</v>
+        <v>0.204382689720462</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>(0.49001536098310294, 'large')</t>
+          <t>(0.1607843137254902, 'small')</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>13.1014652014652</v>
+        <v>3.916666666666667</v>
       </c>
       <c r="I33" t="n">
-        <v>12.65476190476191</v>
+        <v>3.75</v>
       </c>
       <c r="J33" t="n">
-        <v>0.471378034094958</v>
+        <v>0.5154181669270358</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>(0.0125, 'negligible')</t>
+          <t>(-0.005208333333333333, 'negligible')</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>12.16575091575092</v>
+        <v>3.882352941176471</v>
       </c>
       <c r="M33" t="n">
-        <v>13.52798663324979</v>
+        <v>3.909090909090909</v>
       </c>
       <c r="N33" t="n">
-        <v>0.7668416830286695</v>
+        <v>0.553589883372229</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>(-0.09851551956815115, 'negligible')</t>
+          <t>(-0.020053475935828877, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -2341,48 +2341,48 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11.91709695926563</v>
+        <v>2.819277108433735</v>
       </c>
       <c r="D34" t="n">
-        <v>6.130385487528345</v>
+        <v>3.186440677966102</v>
       </c>
       <c r="E34" t="n">
-        <v>13.87711213517665</v>
+        <v>2.875</v>
       </c>
       <c r="F34" t="n">
-        <v>5.506198067795035e-06</v>
+        <v>0.06994480294336693</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>(0.6451612903225806, 'large')</t>
+          <t>(0.2277542372881356, 'small')</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>11.58241758241758</v>
+        <v>3.051724137931035</v>
       </c>
       <c r="I34" t="n">
-        <v>13.11904761904762</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8100980712412638</v>
+        <v>0.8998849873759899</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>(-0.14134615384615384, 'negligible')</t>
+          <t>(-0.20114942528735633, 'small')</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>13.06318681318681</v>
+        <v>3.125</v>
       </c>
       <c r="M34" t="n">
-        <v>11.39431913116124</v>
+        <v>3.117647058823529</v>
       </c>
       <c r="N34" t="n">
-        <v>0.167866036982508</v>
+        <v>0.5721063028071289</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>(0.1329284750337382, 'negligible')</t>
+          <t>(-0.02369281045751634, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -2398,48 +2398,48 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8.53356282271945</v>
+        <v>1.855421686746988</v>
       </c>
       <c r="D35" t="n">
-        <v>1.689342403628118</v>
+        <v>2.803921568627451</v>
       </c>
       <c r="E35" t="n">
-        <v>10.85176651305683</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="F35" t="n">
-        <v>6.45794210942026e-07</v>
+        <v>0.01595814319922114</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>(0.6996927803379416, 'large')</t>
+          <t>(0.5163398692810458, 'large')</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8.039194139194139</v>
+        <v>2.533333333333333</v>
       </c>
       <c r="I35" t="n">
-        <v>10.35863095238095</v>
+        <v>3.363636363636364</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8607420593750961</v>
+        <v>0.9954329602934833</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>(-0.17211538461538461, 'small')</t>
+          <t>(-0.48484848484848486, 'large')</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>9.097069597069597</v>
+        <v>2.9375</v>
       </c>
       <c r="M35" t="n">
-        <v>8.276524644945697</v>
+        <v>2.609756097560976</v>
       </c>
       <c r="N35" t="n">
-        <v>0.4112293309449383</v>
+        <v>0.09409094751979175</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>(0.0310391363022942, 'negligible')</t>
+          <t>(0.21646341463414634, 'small')</t>
         </is>
       </c>
     </row>
@@ -2455,48 +2455,48 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8.552208835341366</v>
+        <v>1.855421686746988</v>
       </c>
       <c r="D36" t="n">
-        <v>2.468253968253968</v>
+        <v>2.957446808510638</v>
       </c>
       <c r="E36" t="n">
-        <v>10.61290322580645</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="F36" t="n">
-        <v>3.902019562108364e-05</v>
+        <v>0.02453726294407041</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>(0.5675883256528418, 'large')</t>
+          <t>(0.44680851063829785, 'medium')</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>8.523076923076923</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="I36" t="n">
-        <v>8.489583333333332</v>
+        <v>2.818181818181818</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5169111170987678</v>
+        <v>0.3915703621429372</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>(-0.0057692307692307696, 'negligible')</t>
+          <t>(0.05411255411255411, 'negligible')</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>8.70970695970696</v>
+        <v>3.066666666666667</v>
       </c>
       <c r="M36" t="n">
-        <v>8.480367585630741</v>
+        <v>2.769230769230769</v>
       </c>
       <c r="N36" t="n">
-        <v>0.5459340109320813</v>
+        <v>0.2007368542164462</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>(-0.014844804318488529, 'negligible')</t>
+          <t>(0.14358974358974358, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -2512,48 +2512,48 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8.78657487091222</v>
+        <v>1.939759036144578</v>
       </c>
       <c r="D37" t="n">
-        <v>2.985260770975056</v>
+        <v>2.648148148148148</v>
       </c>
       <c r="E37" t="n">
-        <v>10.75153609831029</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>3.089022198740768e-06</v>
+        <v>0.02565842388250469</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>(0.6589861751152074, 'large')</t>
+          <t>(0.39094650205761317, 'medium')</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>8.819413919413918</v>
+        <v>2.591836734693878</v>
       </c>
       <c r="I37" t="n">
-        <v>8.501488095238095</v>
+        <v>2.384615384615385</v>
       </c>
       <c r="J37" t="n">
-        <v>0.4714451195844765</v>
+        <v>0.1657909000719572</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>(0.0125, 'negligible')</t>
+          <t>(0.1695447409733124, 'small')</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>9.740842490842491</v>
+        <v>2.523809523809524</v>
       </c>
       <c r="M37" t="n">
-        <v>8.351294903926483</v>
+        <v>2.571428571428572</v>
       </c>
       <c r="N37" t="n">
-        <v>0.244428425955267</v>
+        <v>0.5152639865963633</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>(0.0951417004048583, 'negligible')</t>
+          <t>(-0.0045351473922902496, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -2569,48 +2569,48 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8.119334480780264</v>
+        <v>1.72289156626506</v>
       </c>
       <c r="D38" t="n">
-        <v>2.556689342403628</v>
+        <v>2.415094339622641</v>
       </c>
       <c r="E38" t="n">
-        <v>10.00345622119816</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="F38" t="n">
-        <v>1.040640654634214e-05</v>
+        <v>0.03193624110961106</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>(0.619815668202765, 'large')</t>
+          <t>(0.37735849056603776, 'medium')</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>7.883150183150184</v>
+        <v>2.304347826086957</v>
       </c>
       <c r="I38" t="n">
-        <v>8.578869047619047</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7350872885294439</v>
+        <v>0.4531394344187425</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>(-0.1, 'negligible')</t>
+          <t>(0.021739130434782608, 'negligible')</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>9.477106227106228</v>
+        <v>2.380952380952381</v>
       </c>
       <c r="M38" t="n">
-        <v>7.5</v>
+        <v>2.268292682926829</v>
       </c>
       <c r="N38" t="n">
-        <v>0.1563281420114369</v>
+        <v>0.3528767218534068</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>(0.13832658569500675, 'negligible')</t>
+          <t>(0.05807200929152149, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -2626,48 +2626,48 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8.78829604130809</v>
+        <v>1.975903614457831</v>
       </c>
       <c r="D39" t="n">
-        <v>3.531746031746032</v>
+        <v>2.784313725490196</v>
       </c>
       <c r="E39" t="n">
-        <v>10.56874039938556</v>
+        <v>2.444444444444445</v>
       </c>
       <c r="F39" t="n">
-        <v>5.685319691925949e-05</v>
+        <v>0.162542384450883</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>(0.5606758832565284, 'large')</t>
+          <t>(0.20043572984749455, 'small')</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>8.093772893772893</v>
+        <v>2.636363636363636</v>
       </c>
       <c r="I39" t="n">
-        <v>11.06101190476191</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9511434130059856</v>
+        <v>0.8859900468009847</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>(-0.2644230769230769, 'small')</t>
+          <t>(-0.20454545454545456, 'small')</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>8.566849816849816</v>
+        <v>2.705882352941177</v>
       </c>
       <c r="M39" t="n">
-        <v>8.889306599832915</v>
+        <v>2.744186046511628</v>
       </c>
       <c r="N39" t="n">
-        <v>0.5922038551896573</v>
+        <v>0.5307362726922537</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>(-0.0310391363022942, 'negligible')</t>
+          <t>(-0.01094391244870041, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -2683,48 +2683,48 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11.66781411359725</v>
+        <v>2.63855421686747</v>
       </c>
       <c r="D40" t="n">
-        <v>5.503401360544217</v>
+        <v>3.303571428571428</v>
       </c>
       <c r="E40" t="n">
-        <v>13.75576036866359</v>
+        <v>2.615384615384615</v>
       </c>
       <c r="F40" t="n">
-        <v>1.18772830595962e-05</v>
+        <v>0.002929970720970216</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>(0.6190476190476191, 'large')</t>
+          <t>(0.46016483516483514, 'medium')</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>11.2974358974359</v>
+        <v>3.115384615384615</v>
       </c>
       <c r="I40" t="n">
-        <v>12.98363095238095</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8262785981736198</v>
+        <v>0.8652183920720244</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>(-0.15096153846153845, 'small')</t>
+          <t>(-0.17307692307692307, 'small')</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>11.66117216117216</v>
+        <v>3.315789473684211</v>
       </c>
       <c r="M40" t="n">
-        <v>11.67084377610693</v>
+        <v>3.12</v>
       </c>
       <c r="N40" t="n">
-        <v>0.4413181439216848</v>
+        <v>0.2113783979515971</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>(0.020917678812415654, 'negligible')</t>
+          <t>(0.11789473684210526, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -2740,48 +2740,48 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11.5697074010327</v>
+        <v>2.602409638554217</v>
       </c>
       <c r="D41" t="n">
-        <v>4.815192743764172</v>
+        <v>3.066666666666667</v>
       </c>
       <c r="E41" t="n">
-        <v>13.85752688172043</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="F41" t="n">
-        <v>2.021913216691479e-06</v>
+        <v>0.1056038459021088</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>(0.6758832565284179, 'large')</t>
+          <t>(0.21944444444444444, 'small')</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>11.07545787545788</v>
+        <v>2.944444444444445</v>
       </c>
       <c r="I41" t="n">
-        <v>13.37648809523809</v>
+        <v>3.1875</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8825310149793462</v>
+        <v>0.7763735580887685</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>(-0.19134615384615383, 'small')</t>
+          <t>(-0.11805555555555555, 'negligible')</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>13.04120879120879</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="M41" t="n">
-        <v>10.8984962406015</v>
+        <v>3.041666666666667</v>
       </c>
       <c r="N41" t="n">
-        <v>0.1568366609612849</v>
+        <v>0.6448454249616042</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>(0.13900134952766532, 'negligible')</t>
+          <t>(-0.050347222222222224, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -2797,48 +2797,48 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6.808089500860585</v>
+        <v>1.44578313253012</v>
       </c>
       <c r="D42" t="n">
-        <v>1.172335600907029</v>
+        <v>2.85</v>
       </c>
       <c r="E42" t="n">
-        <v>8.716973886328725</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>3.883647707593069e-05</v>
+        <v>0.144420139805331</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>(0.5468509984639017, 'large')</t>
+          <t>(0.35833333333333334, 'medium')</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>6.548351648351648</v>
+        <v>2.787878787878788</v>
       </c>
       <c r="I42" t="n">
-        <v>7.464285714285714</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6770138310700133</v>
+        <v>0.4935434651170891</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>(-0.06923076923076923, 'negligible')</t>
+          <t>(0.006734006734006734, 'negligible')</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>8.155677655677653</v>
+        <v>2.6875</v>
       </c>
       <c r="M42" t="n">
-        <v>6.193400167084378</v>
+        <v>2.851851851851852</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1837435975468885</v>
+        <v>0.6600542816943267</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>(0.11740890688259109, 'negligible')</t>
+          <t>(-0.06944444444444445, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -2854,48 +2854,48 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7.935456110154905</v>
+        <v>1.710843373493976</v>
       </c>
       <c r="D43" t="n">
-        <v>1.900226757369614</v>
+        <v>2.673469387755102</v>
       </c>
       <c r="E43" t="n">
-        <v>9.979646697388629</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="F43" t="n">
-        <v>6.24037909066429e-06</v>
+        <v>0.02453087017465394</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>(0.6290322580645161, 'large')</t>
+          <t>(0.47959183673469385, 'large')</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>7.626007326007326</v>
+        <v>2.560975609756098</v>
       </c>
       <c r="I43" t="n">
-        <v>8.669642857142858</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="J43" t="n">
-        <v>0.681716974434829</v>
+        <v>0.6381899412928471</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>(-0.07403846153846154, 'negligible')</t>
+          <t>(-0.06300813008130081, 'negligible')</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>8.280219780219779</v>
+        <v>2.588235294117647</v>
       </c>
       <c r="M43" t="n">
-        <v>7.778195488721804</v>
+        <v>2.578947368421053</v>
       </c>
       <c r="N43" t="n">
-        <v>0.4245616515007434</v>
+        <v>0.4924337521051868</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>(0.02631578947368421, 'negligible')</t>
+          <t>(0.0046439628482972135, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -2911,48 +2911,48 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10.24096385542169</v>
+        <v>2.409638554216868</v>
       </c>
       <c r="D44" t="n">
-        <v>5.484126984126983</v>
+        <v>3.24</v>
       </c>
       <c r="E44" t="n">
-        <v>11.85215053763441</v>
+        <v>3.454545454545455</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0009065469067758631</v>
+        <v>0.7109626446406618</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>(0.4539170506912442, 'medium')</t>
+          <t>(-0.09454545454545454, 'negligible')</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>9.752014652014651</v>
+        <v>3.148936170212766</v>
       </c>
       <c r="I44" t="n">
-        <v>11.72767857142857</v>
+        <v>3.75</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8091463447630078</v>
+        <v>0.9571694596371743</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>(-0.13942307692307693, 'negligible')</t>
+          <t>(-0.2872340425531915, 'small')</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>10.36172161172161</v>
+        <v>3.052631578947369</v>
       </c>
       <c r="M44" t="n">
-        <v>10.1858813700919</v>
+        <v>3.380952380952381</v>
       </c>
       <c r="N44" t="n">
-        <v>0.5059305570809184</v>
+        <v>0.9600424168616428</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>(-0.001349527665317139, 'negligible')</t>
+          <t>(-0.2506265664160401, 'small')</t>
         </is>
       </c>
     </row>
@@ -2968,48 +2968,48 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6.429718875502008</v>
+        <v>1.469879518072289</v>
       </c>
       <c r="D45" t="n">
-        <v>2.83219954648526</v>
+        <v>2.891891891891892</v>
       </c>
       <c r="E45" t="n">
-        <v>7.648233486943165</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>0.00349415907871644</v>
+        <v>0.6125956653792488</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>(0.3717357910906298, 'medium')</t>
+          <t>(-0.07027027027027027, 'negligible')</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5.582783882783883</v>
+        <v>2.766666666666667</v>
       </c>
       <c r="I45" t="n">
-        <v>9.424107142857142</v>
+        <v>3.272727272727273</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9685048185533154</v>
+        <v>0.8426130714636795</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>(-0.28173076923076923, 'small')</t>
+          <t>(-0.19393939393939394, 'small')</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5.794871794871795</v>
+        <v>2.818181818181818</v>
       </c>
       <c r="M45" t="n">
-        <v>6.719298245614035</v>
+        <v>2.935483870967742</v>
       </c>
       <c r="N45" t="n">
-        <v>0.7697646840650902</v>
+        <v>0.6632854400493733</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>(-0.09446693657219973, 'negligible')</t>
+          <t>(-0.07917888563049853, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3025,48 +3025,48 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>9.039300057372346</v>
+        <v>2.084337349397591</v>
       </c>
       <c r="D46" t="n">
-        <v>4.202947845804989</v>
+        <v>2.959183673469388</v>
       </c>
       <c r="E46" t="n">
-        <v>10.67741935483871</v>
+        <v>2.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0004107094296265491</v>
+        <v>0.2652836868509597</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>(0.48540706605222733, 'large')</t>
+          <t>(0.12244897959183673, 'negligible')</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8.676923076923076</v>
+        <v>2.847826086956522</v>
       </c>
       <c r="I46" t="n">
-        <v>10.39136904761905</v>
+        <v>3.25</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7995532379885122</v>
+        <v>0.877564821973723</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>(-0.13365384615384615, 'negligible')</t>
+          <t>(-0.20652173913043478, 'small')</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>9.268315018315018</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="M46" t="n">
-        <v>8.934837092731831</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>0.4722669505740849</v>
+        <v>0.7946954742885463</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>(0.010121457489878543, 'negligible')</t>
+          <t>(-0.12737127371273713, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3082,48 +3082,48 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>9.70166379804934</v>
+        <v>2.265060240963856</v>
       </c>
       <c r="D47" t="n">
-        <v>5.308390022675736</v>
+        <v>3.208333333333333</v>
       </c>
       <c r="E47" t="n">
-        <v>11.18970814132105</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="F47" t="n">
-        <v>0.002593081504956445</v>
+        <v>0.103383185140217</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>(0.4062980030721966, 'medium')</t>
+          <t>(0.2222222222222222, 'small')</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.053113553113553</v>
+        <v>3.044444444444444</v>
       </c>
       <c r="I47" t="n">
-        <v>12.03422619047619</v>
+        <v>3.538461538461538</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8939916825220053</v>
+        <v>0.9422103608738299</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>(-0.19903846153846153, 'small')</t>
+          <t>(-0.26495726495726496, 'small')</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>9.952380952380953</v>
+        <v>3.052631578947369</v>
       </c>
       <c r="M47" t="n">
-        <v>9.587301587301585</v>
+        <v>3.170731707317073</v>
       </c>
       <c r="N47" t="n">
-        <v>0.390553002554837</v>
+        <v>0.7583326063409297</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>(0.038461538461538464, 'negligible')</t>
+          <t>(-0.10397946084724005, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3139,48 +3139,48 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5.54302925989673</v>
+        <v>1.180722891566265</v>
       </c>
       <c r="D48" t="n">
-        <v>1.852607709750567</v>
+        <v>1.914893617021277</v>
       </c>
       <c r="E48" t="n">
-        <v>6.793010752688171</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>2.117136432589914e-05</v>
+        <v>0.5300216790615842</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>(0.5837173579109063, 'large')</t>
+          <t>(-0.015957446808510637, 'negligible')</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>5.038827838827839</v>
+        <v>1.769230769230769</v>
       </c>
       <c r="I48" t="n">
-        <v>7.03422619047619</v>
+        <v>2.363636363636364</v>
       </c>
       <c r="J48" t="n">
-        <v>0.871916666555085</v>
+        <v>0.9523271422105293</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>(-0.1778846153846154, 'small')</t>
+          <t>(-0.30536130536130535, 'small')</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>5.402930402930404</v>
+        <v>1.8125</v>
       </c>
       <c r="M48" t="n">
-        <v>5.606934001670844</v>
+        <v>1.971428571428572</v>
       </c>
       <c r="N48" t="n">
-        <v>0.4878991730018694</v>
+        <v>0.7073105357695193</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>(0.004723346828609987, 'negligible')</t>
+          <t>(-0.0875, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3196,48 +3196,48 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7.574584050487665</v>
+        <v>1.614457831325301</v>
       </c>
       <c r="D49" t="n">
-        <v>2.873015873015873</v>
+        <v>2.727272727272727</v>
       </c>
       <c r="E49" t="n">
-        <v>9.16705069124424</v>
+        <v>2.8</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0002622135289271947</v>
+        <v>0.5274961299591371</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>(0.4915514592933948, 'large')</t>
+          <t>(-0.013636363636363636, 'negligible')</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>7.15018315018315</v>
+        <v>2.631578947368421</v>
       </c>
       <c r="I49" t="n">
-        <v>8.995535714285714</v>
+        <v>3.1</v>
       </c>
       <c r="J49" t="n">
-        <v>0.7713268685635728</v>
+        <v>0.9238034411364168</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>(-0.11538461538461539, 'negligible')</t>
+          <t>(-0.28157894736842104, 'small')</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>7.336996336996338</v>
+        <v>2.6</v>
       </c>
       <c r="M49" t="n">
-        <v>7.68295739348371</v>
+        <v>2.794117647058823</v>
       </c>
       <c r="N49" t="n">
-        <v>0.5806187370140239</v>
+        <v>0.7726215816398327</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>(-0.02631578947368421, 'negligible')</t>
+          <t>(-0.12745098039215685, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3253,48 +3253,48 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>18.6956397016638</v>
+        <v>4.445783132530121</v>
       </c>
       <c r="D50" t="n">
-        <v>12.41950113378685</v>
+        <v>4.548387096774194</v>
       </c>
       <c r="E50" t="n">
-        <v>20.82142857142857</v>
+        <v>4.142857142857143</v>
       </c>
       <c r="F50" t="n">
-        <v>4.686302000289633e-06</v>
+        <v>0.128837353896481</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>(0.6505376344086021, 'large')</t>
+          <t>(0.14516129032258066, 'negligible')</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>18.50769230769231</v>
+        <v>4.384615384615385</v>
       </c>
       <c r="I50" t="n">
-        <v>19.46726190476191</v>
+        <v>4.6875</v>
       </c>
       <c r="J50" t="n">
-        <v>0.6950152587125997</v>
+        <v>0.908389110141675</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>(-0.08173076923076923, 'negligible')</t>
+          <t>(-0.18653846153846154, 'small')</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>19.37545787545788</v>
+        <v>4.346153846153846</v>
       </c>
       <c r="M50" t="n">
-        <v>18.38554720133667</v>
+        <v>4.491228070175438</v>
       </c>
       <c r="N50" t="n">
-        <v>0.3916863016380008</v>
+        <v>0.937605369017222</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>(0.038461538461538464, 'negligible')</t>
+          <t>(-0.18286099865047234, 'small')</t>
         </is>
       </c>
     </row>
@@ -3310,48 +3310,48 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>17.94348823866896</v>
+        <v>4.228915662650603</v>
       </c>
       <c r="D51" t="n">
-        <v>12.5328798185941</v>
+        <v>4.32258064516129</v>
       </c>
       <c r="E51" t="n">
-        <v>19.77611367127496</v>
+        <v>3.952380952380953</v>
       </c>
       <c r="F51" t="n">
-        <v>9.602089711977958e-05</v>
+        <v>0.2261097113360939</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>(0.5476190476190477, 'large')</t>
+          <t>(0.10215053763440861, 'negligible')</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>17.70549450549451</v>
+        <v>4.123076923076923</v>
       </c>
       <c r="I51" t="n">
-        <v>18.40773809523809</v>
+        <v>4.5625</v>
       </c>
       <c r="J51" t="n">
-        <v>0.6631729756557481</v>
+        <v>0.9597347927988793</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>(-0.0673076923076923, 'negligible')</t>
+          <t>(-0.2605769230769231, 'small')</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>18.76923076923077</v>
+        <v>4.192307692307693</v>
       </c>
       <c r="M51" t="n">
-        <v>17.56683375104428</v>
+        <v>4.245614035087719</v>
       </c>
       <c r="N51" t="n">
-        <v>0.3527078104383267</v>
+        <v>0.7757654910794362</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>(0.05263157894736842, 'negligible')</t>
+          <t>(-0.0951417004048583, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3367,48 +3367,48 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>16.98221457257602</v>
+        <v>4.048192771084337</v>
       </c>
       <c r="D52" t="n">
-        <v>12.72335600907029</v>
+        <v>4.064516129032258</v>
       </c>
       <c r="E52" t="n">
-        <v>18.4247311827957</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0006741270684240462</v>
+        <v>0.6878676187783185</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>(0.47081413210445466, 'medium')</t>
+          <t>(-0.06682027649769585, 'negligible')</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>17.06849816849817</v>
+        <v>4.046153846153846</v>
       </c>
       <c r="I52" t="n">
-        <v>16.00892857142857</v>
+        <v>3.9375</v>
       </c>
       <c r="J52" t="n">
-        <v>0.2667034529376008</v>
+        <v>0.285341217851656</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>(0.10192307692307692, 'negligible')</t>
+          <t>(0.0875, 'negligible')</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>18.3040293040293</v>
+        <v>4.153846153846154</v>
       </c>
       <c r="M52" t="n">
-        <v>16.37928153717628</v>
+        <v>4</v>
       </c>
       <c r="N52" t="n">
-        <v>0.1729426010419025</v>
+        <v>0.3064070242872721</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>(0.13022941970310392, 'negligible')</t>
+          <t>(0.06612685560053981, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3424,48 +3424,48 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>17.88209982788296</v>
+        <v>4.253012048192771</v>
       </c>
       <c r="D53" t="n">
-        <v>13.70975056689342</v>
+        <v>4.258064516129032</v>
       </c>
       <c r="E53" t="n">
-        <v>19.29531490015361</v>
+        <v>4.238095238095238</v>
       </c>
       <c r="F53" t="n">
-        <v>0.002664272127875927</v>
+        <v>0.7568748714575558</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>(0.4093701996927803, 'medium')</t>
+          <t>(-0.09293394777265745, 'negligible')</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>17.94761904761905</v>
+        <v>4.246153846153846</v>
       </c>
       <c r="I53" t="n">
-        <v>17.65476190476191</v>
+        <v>4.3125</v>
       </c>
       <c r="J53" t="n">
-        <v>0.3970512063227751</v>
+        <v>0.63922928975339</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>(0.04326923076923077, 'negligible')</t>
+          <t>(-0.051923076923076926, 'negligible')</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>18.92490842490842</v>
+        <v>4.269230769230769</v>
       </c>
       <c r="M53" t="n">
-        <v>17.40643274853801</v>
+        <v>4.245614035087719</v>
       </c>
       <c r="N53" t="n">
-        <v>0.2506068457427092</v>
+        <v>0.6177469975908975</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>(0.0931174089068826, 'negligible')</t>
+          <t>(-0.037112010796221326, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3481,48 +3481,48 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>18.51118760757315</v>
+        <v>4.36144578313253</v>
       </c>
       <c r="D54" t="n">
-        <v>13.22335600907029</v>
+        <v>4.435483870967742</v>
       </c>
       <c r="E54" t="n">
-        <v>20.30222734254992</v>
+        <v>4.142857142857143</v>
       </c>
       <c r="F54" t="n">
-        <v>0.000110979186156683</v>
+        <v>0.3537663622762965</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>(0.5422427035330261, 'large')</t>
+          <t>(0.04992319508448541, 'negligible')</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>18.71501831501831</v>
+        <v>4.4</v>
       </c>
       <c r="I54" t="n">
-        <v>17.66815476190476</v>
+        <v>4.1875</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3455309110863635</v>
+        <v>0.1425849370009574</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>(0.06538461538461539, 'negligible')</t>
+          <t>(0.15576923076923077, 'small')</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>19.74816849816849</v>
+        <v>4.5</v>
       </c>
       <c r="M54" t="n">
-        <v>17.9469507101086</v>
+        <v>4.298245614035087</v>
       </c>
       <c r="N54" t="n">
-        <v>0.2233423737203955</v>
+        <v>0.289464830135199</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>(0.10526315789473684, 'negligible')</t>
+          <t>(0.06882591093117409, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3538,48 +3538,48 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>18.38095238095238</v>
+        <v>4.373493975903615</v>
       </c>
       <c r="D55" t="n">
-        <v>14.32766439909297</v>
+        <v>4.306451612903226</v>
       </c>
       <c r="E55" t="n">
-        <v>19.75384024577573</v>
+        <v>4.571428571428571</v>
       </c>
       <c r="F55" t="n">
-        <v>0.002416742952951279</v>
+        <v>0.9607141335909734</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>(0.41397849462365593, 'medium')</t>
+          <t>(-0.22964669738863286, 'small')</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>18.27435897435897</v>
+        <v>4.323076923076923</v>
       </c>
       <c r="I55" t="n">
-        <v>18.36607142857143</v>
+        <v>4.5</v>
       </c>
       <c r="J55" t="n">
-        <v>0.4621949471447785</v>
+        <v>0.7519789856787016</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>(0.016346153846153847, 'negligible')</t>
+          <t>(-0.09807692307692308, 'negligible')</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>19.41300366300366</v>
+        <v>4.346153846153846</v>
       </c>
       <c r="M55" t="n">
-        <v>17.91019214703425</v>
+        <v>4.385964912280702</v>
       </c>
       <c r="N55" t="n">
-        <v>0.2277644137658337</v>
+        <v>0.7982447964017445</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>(0.10323886639676114, 'negligible')</t>
+          <t>(-0.101889338731444, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3595,48 +3595,48 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>18.92484222604704</v>
+        <v>4.493975903614458</v>
       </c>
       <c r="D56" t="n">
-        <v>13.79931972789115</v>
+        <v>4.5</v>
       </c>
       <c r="E56" t="n">
-        <v>20.66090629800307</v>
+        <v>4.476190476190476</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0003250148661585268</v>
+        <v>0.851791699538244</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>(0.500768049155146, 'large')</t>
+          <t>(-0.1282642089093702, 'negligible')</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>19.02490842490842</v>
+        <v>4.476923076923077</v>
       </c>
       <c r="I56" t="n">
-        <v>18.55505952380953</v>
+        <v>4.5625</v>
       </c>
       <c r="J56" t="n">
-        <v>0.4363795566643975</v>
+        <v>0.6029936460426667</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>(0.026923076923076925, 'negligible')</t>
+          <t>(-0.03461538461538462, 'negligible')</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>19.63644688644689</v>
+        <v>4.423076923076923</v>
       </c>
       <c r="M56" t="n">
-        <v>18.60025062656642</v>
+        <v>4.526315789473684</v>
       </c>
       <c r="N56" t="n">
-        <v>0.3748197977531433</v>
+        <v>0.8958604604887915</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>(0.044534412955465584, 'negligible')</t>
+          <t>(-0.14507422402159245, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3652,48 +3652,48 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>18.19219736087206</v>
+        <v>4.301204819277109</v>
       </c>
       <c r="D57" t="n">
-        <v>12.95578231292517</v>
+        <v>4.354838709677419</v>
       </c>
       <c r="E57" t="n">
-        <v>19.965821812596</v>
+        <v>4.142857142857143</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0002337093725339319</v>
+        <v>0.6654803494745041</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>(0.5138248847926268, 'large')</t>
+          <t>(-0.055299539170506916, 'negligible')</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>18.04139194139194</v>
+        <v>4.215384615384616</v>
       </c>
       <c r="I57" t="n">
-        <v>18.33333333333334</v>
+        <v>4.5625</v>
       </c>
       <c r="J57" t="n">
-        <v>0.5212866781959314</v>
+        <v>0.8371314219698275</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>(-0.007692307692307693, 'negligible')</t>
+          <t>(-0.1423076923076923, 'negligible')</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>19.24267399267399</v>
+        <v>4.307692307692307</v>
       </c>
       <c r="M57" t="n">
-        <v>17.71303258145363</v>
+        <v>4.298245614035087</v>
       </c>
       <c r="N57" t="n">
-        <v>0.2521737423022089</v>
+        <v>0.6873967381587979</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>(0.09244264507422402, 'negligible')</t>
+          <t>(-0.059379217273954114, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3709,48 +3709,48 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>14.12248995983936</v>
+        <v>3.385542168674699</v>
       </c>
       <c r="D58" t="n">
-        <v>10.08956916099773</v>
+        <v>3.435483870967742</v>
       </c>
       <c r="E58" t="n">
-        <v>15.48847926267281</v>
+        <v>3.238095238095238</v>
       </c>
       <c r="F58" t="n">
-        <v>0.001622244023535598</v>
+        <v>0.3695867991013105</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>(0.4324116743471582, 'medium')</t>
+          <t>(0.047619047619047616, 'negligible')</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>14.30622710622711</v>
+        <v>3.415384615384615</v>
       </c>
       <c r="I58" t="n">
-        <v>13.36160714285714</v>
+        <v>3.25</v>
       </c>
       <c r="J58" t="n">
-        <v>0.2946803144383829</v>
+        <v>0.2582904189593527</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>(0.08846153846153847, 'negligible')</t>
+          <t>(0.10192307692307692, 'negligible')</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>16.04120879120879</v>
+        <v>3.692307692307693</v>
       </c>
       <c r="M58" t="n">
-        <v>13.24728487886383</v>
+        <v>3.245614035087719</v>
       </c>
       <c r="N58" t="n">
-        <v>0.02654029855670663</v>
+        <v>0.07822344636228454</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>(0.26653171390013497, 'small')</t>
+          <t>(0.18758434547908232, 'small')</t>
         </is>
       </c>
     </row>
@@ -3766,48 +3766,48 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>17.41107286288009</v>
+        <v>4.120481927710843</v>
       </c>
       <c r="D59" t="n">
-        <v>12.94331065759637</v>
+        <v>4.161290322580645</v>
       </c>
       <c r="E59" t="n">
-        <v>18.92434715821812</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
-        <v>0.00113070741204583</v>
+        <v>0.730282383842335</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>(0.4485407066052227, 'medium')</t>
+          <t>(-0.08294930875576037, 'negligible')</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>17.41098901098901</v>
+        <v>4.092307692307692</v>
       </c>
       <c r="I59" t="n">
-        <v>17.25892857142857</v>
+        <v>4.1875</v>
       </c>
       <c r="J59" t="n">
-        <v>0.466909696136138</v>
+        <v>0.4670113181967164</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>(0.014423076923076924, 'negligible')</t>
+          <t>(0.013461538461538462, 'negligible')</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>18.63553113553114</v>
+        <v>4.192307692307693</v>
       </c>
       <c r="M59" t="n">
-        <v>16.85254803675856</v>
+        <v>4.087719298245614</v>
       </c>
       <c r="N59" t="n">
-        <v>0.2382792465697897</v>
+        <v>0.5958975271501471</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>(0.09851551956815115, 'negligible')</t>
+          <t>(-0.030364372469635626, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3823,48 +3823,48 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>18.87320711417097</v>
+        <v>4.469879518072289</v>
       </c>
       <c r="D60" t="n">
-        <v>13.45351473922902</v>
+        <v>4.532258064516129</v>
       </c>
       <c r="E60" t="n">
-        <v>20.70890937019969</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0001334481533753704</v>
+        <v>0.5631377144413664</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>(0.5353302611367128, 'large')</t>
+          <t>(-0.018433179723502304, 'negligible')</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>18.85567765567765</v>
+        <v>4.430769230769231</v>
       </c>
       <c r="I60" t="n">
-        <v>18.97470238095238</v>
+        <v>4.625</v>
       </c>
       <c r="J60" t="n">
-        <v>0.5636193747691292</v>
+        <v>0.5745041037720968</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>(-0.025, 'negligible')</t>
+          <t>(-0.02403846153846154, 'negligible')</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>20.13003663003663</v>
+        <v>4.5</v>
       </c>
       <c r="M60" t="n">
-        <v>18.29991645781119</v>
+        <v>4.456140350877193</v>
       </c>
       <c r="N60" t="n">
-        <v>0.2979821739509313</v>
+        <v>0.9174858844691021</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>(0.07354925775978408, 'negligible')</t>
+          <t>(-0.15654520917678813, 'small')</t>
         </is>
       </c>
     </row>
@@ -3880,48 +3880,48 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>16.04016064257028</v>
+        <v>3.843373493975904</v>
       </c>
       <c r="D61" t="n">
-        <v>11.47392290249433</v>
+        <v>3.887096774193548</v>
       </c>
       <c r="E61" t="n">
-        <v>17.58678955453149</v>
+        <v>3.714285714285714</v>
       </c>
       <c r="F61" t="n">
-        <v>0.001092031877530336</v>
+        <v>0.5502162531517411</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>(0.4500768049155146, 'medium')</t>
+          <t>(-0.016897081413210446, 'negligible')</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>16.29597069597069</v>
+        <v>3.861538461538462</v>
       </c>
       <c r="I61" t="n">
-        <v>15.09375</v>
+        <v>3.75</v>
       </c>
       <c r="J61" t="n">
-        <v>0.2328304667271552</v>
+        <v>0.187143127081898</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>(0.11923076923076924, 'negligible')</t>
+          <t>(0.13846153846153847, 'negligible')</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>17.47435897435897</v>
+        <v>3.961538461538462</v>
       </c>
       <c r="M61" t="n">
-        <v>15.3859649122807</v>
+        <v>3.789473684210526</v>
       </c>
       <c r="N61" t="n">
-        <v>0.1594860439264189</v>
+        <v>0.4672071170463282</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>(0.13765182186234817, 'negligible')</t>
+          <t>(0.011470985155195682, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3937,48 +3937,48 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>18.08548479632817</v>
+        <v>4.27710843373494</v>
       </c>
       <c r="D62" t="n">
-        <v>13.54195011337868</v>
+        <v>4.274193548387097</v>
       </c>
       <c r="E62" t="n">
-        <v>19.62442396313364</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0009652072415384667</v>
+        <v>0.8154264066615253</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>(0.4554531490015361, 'medium')</t>
+          <t>(-0.11827956989247312, 'negligible')</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>18.11465201465202</v>
+        <v>4.261538461538461</v>
       </c>
       <c r="I62" t="n">
-        <v>17.89880952380953</v>
+        <v>4.3125</v>
       </c>
       <c r="J62" t="n">
-        <v>0.4200866187126104</v>
+        <v>0.5521983478094028</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>(0.03365384615384615, 'negligible')</t>
+          <t>(-0.01826923076923077, 'negligible')</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>19.2985347985348</v>
+        <v>4.269230769230769</v>
       </c>
       <c r="M62" t="n">
-        <v>17.53216374269006</v>
+        <v>4.280701754385965</v>
       </c>
       <c r="N62" t="n">
-        <v>0.2521715051221769</v>
+        <v>0.7302853369684611</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>(0.09244264507422402, 'negligible')</t>
+          <t>(-0.07557354925775979, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -3994,48 +3994,48 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>18.38726333907057</v>
+        <v>4.409638554216867</v>
       </c>
       <c r="D63" t="n">
-        <v>14.25056689342404</v>
+        <v>4.354838709677419</v>
       </c>
       <c r="E63" t="n">
-        <v>19.7884024577573</v>
+        <v>4.571428571428571</v>
       </c>
       <c r="F63" t="n">
-        <v>0.001072834543743844</v>
+        <v>0.956274468906322</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>(0.4508448540706605, 'medium')</t>
+          <t>(-0.21889400921658986, 'small')</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>18.51611721611722</v>
+        <v>4.415384615384616</v>
       </c>
       <c r="I63" t="n">
-        <v>17.83333333333333</v>
+        <v>4.375</v>
       </c>
       <c r="J63" t="n">
-        <v>0.3743702306654101</v>
+        <v>0.4011094394336732</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>(0.052884615384615384, 'negligible')</t>
+          <t>(0.03653846153846154, 'negligible')</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>19.4496336996337</v>
+        <v>4.384615384615385</v>
       </c>
       <c r="M63" t="n">
-        <v>17.90267335004177</v>
+        <v>4.421052631578948</v>
       </c>
       <c r="N63" t="n">
-        <v>0.2367605650472827</v>
+        <v>0.7916413262262267</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>(0.09919028340080972, 'negligible')</t>
+          <t>(-0.09716599190283401, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -4051,48 +4051,48 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>15.72375215146299</v>
+        <v>3.759036144578313</v>
       </c>
       <c r="D64" t="n">
-        <v>11.02154195011338</v>
+        <v>3.806451612903226</v>
       </c>
       <c r="E64" t="n">
-        <v>17.31643625192012</v>
+        <v>3.619047619047619</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0003716400909887213</v>
+        <v>0.3946861162791896</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>(0.49539170506912444, 'large')</t>
+          <t>(0.03840245775729647, 'negligible')</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>15.65787545787546</v>
+        <v>3.707692307692308</v>
       </c>
       <c r="I64" t="n">
-        <v>16.04464285714285</v>
+        <v>3.9375</v>
       </c>
       <c r="J64" t="n">
-        <v>0.6006599330801025</v>
+        <v>0.7149149765322487</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>(-0.04038461538461539, 'negligible')</t>
+          <t>(-0.0875, 'negligible')</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>16.53754578754579</v>
+        <v>3.807692307692307</v>
       </c>
       <c r="M64" t="n">
-        <v>15.35254803675856</v>
+        <v>3.736842105263158</v>
       </c>
       <c r="N64" t="n">
-        <v>0.2061474203741796</v>
+        <v>0.4230209027059261</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>(0.11336032388663968, 'negligible')</t>
+          <t>(0.02631578947368421, 'negligible')</t>
         </is>
       </c>
     </row>
@@ -4108,48 +4108,48 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>17.55794606999426</v>
+        <v>4.108433734939759</v>
       </c>
       <c r="D65" t="n">
-        <v>11.70975056689342</v>
+        <v>4.225806451612903</v>
       </c>
       <c r="E65" t="n">
-        <v>19.53878648233487</v>
+        <v>3.761904761904762</v>
       </c>
       <c r="F65" t="n">
-        <v>2.877501673681875e-05</v>
+        <v>0.2330637014880765</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>(0.5906298003072197, 'large')</t>
+          <t>(0.09984639016897082, 'negligible')</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>17.4003663003663</v>
+        <v>4.061538461538461</v>
       </c>
       <c r="I65" t="n">
-        <v>17.64732142857143</v>
+        <v>4.1875</v>
       </c>
       <c r="J65" t="n">
-        <v>0.5659551866694463</v>
+        <v>0.6797493540191974</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>(-0.025961538461538463, 'negligible')</t>
+          <t>(-0.06923076923076923, 'negligible')</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>19.51831501831502</v>
+        <v>4.346153846153846</v>
       </c>
       <c r="M65" t="n">
-        <v>16.66374269005848</v>
+        <v>4</v>
       </c>
       <c r="N65" t="n">
-        <v>0.1080108093679032</v>
+        <v>0.1066737669381883</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>(0.17071524966261808, 'small')</t>
+          <t>(0.1592442645074224, 'small')</t>
         </is>
       </c>
     </row>
